--- a/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>mantenimiento</t>
+          <t>Intervenido PI2024</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -555,7 +555,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -815,7 +815,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1058,7 +1058,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1110,7 +1110,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1179,7 +1179,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LEONCIO_PRADO</t>
+          <t>LEONCIO PRADO</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>No</t>
         </is>
       </c>
     </row>

--- a/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,62 +417,62 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>departamento</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>provincia</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>distrito</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>codigo_ce</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>descripcion</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>longitud</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>alumnos</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>docentes</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Intervenido PI2024</t>
         </is>
@@ -521,20 +509,30 @@
           <t>017</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>-9.296760000000001</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-75.99981</v>
-      </c>
-      <c r="I2" t="n">
-        <v>379</v>
-      </c>
-      <c r="J2" t="n">
-        <v>15</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>-9.29676</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>-75.99981</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -573,20 +571,30 @@
           <t>018</t>
         </is>
       </c>
-      <c r="G3" t="n">
-        <v>-9.306462</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-76.003079</v>
-      </c>
-      <c r="I3" t="n">
-        <v>52</v>
-      </c>
-      <c r="J3" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1</v>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>-9.306462</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-76.003079</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -625,20 +633,30 @@
           <t>32262 LEONCIO PRADO GUTIERREZ</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>-9.296469999999999</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-75.9986</v>
-      </c>
-      <c r="I4" t="n">
-        <v>855</v>
-      </c>
-      <c r="J4" t="n">
-        <v>34</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0</v>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-9.29647</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-75.9986</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -677,20 +695,30 @@
           <t>32483 RICARDO PALMA SORIANO</t>
         </is>
       </c>
-      <c r="G5" t="n">
-        <v>-9.302519999999999</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-76.00230000000001</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1655</v>
-      </c>
-      <c r="J5" t="n">
-        <v>64</v>
-      </c>
-      <c r="K5" t="n">
-        <v>0</v>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-9.30252</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-76.0023</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1655</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -729,20 +757,30 @@
           <t>32916 ESTEBAN FLORES LLANOS</t>
         </is>
       </c>
-      <c r="G6" t="n">
-        <v>-9.2944</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-75.9939</v>
-      </c>
-      <c r="I6" t="n">
-        <v>325</v>
-      </c>
-      <c r="J6" t="n">
-        <v>16</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0</v>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-9.2944</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-75.9939</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -781,20 +819,30 @@
           <t>CESAR VALLEJO</t>
         </is>
       </c>
-      <c r="G7" t="n">
-        <v>-9.278459</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-76.00929600000001</v>
-      </c>
-      <c r="I7" t="n">
-        <v>968</v>
-      </c>
-      <c r="J7" t="n">
-        <v>44</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-9.278459</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-76.009296</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>968</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -833,20 +881,30 @@
           <t>GOMEZ ARIAS DAVILA</t>
         </is>
       </c>
-      <c r="G8" t="n">
-        <v>-9.305870000000001</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-76.00341</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2260</v>
-      </c>
-      <c r="J8" t="n">
-        <v>76</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-9.30587</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-76.00341</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2260</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -885,20 +943,30 @@
           <t>MARIANO BONIN</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>-9.292210000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-75.99722</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1432</v>
-      </c>
-      <c r="J9" t="n">
-        <v>63</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0</v>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-9.29221</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-75.99722</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1432</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -937,20 +1005,30 @@
           <t>MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
-      <c r="G10" t="n">
-        <v>-9.30245</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-76.00537</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1494</v>
-      </c>
-      <c r="J10" t="n">
-        <v>58</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-9.30245</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-76.00537</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1494</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -989,20 +1067,30 @@
           <t>PADRE ABAD</t>
         </is>
       </c>
-      <c r="G11" t="n">
-        <v>-9.299770000000001</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-75.9995</v>
-      </c>
-      <c r="I11" t="n">
-        <v>1114</v>
-      </c>
-      <c r="J11" t="n">
-        <v>60</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-9.29977</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-75.9995</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1041,20 +1129,30 @@
           <t>SAN JORGE</t>
         </is>
       </c>
-      <c r="G12" t="n">
-        <v>-9.28735</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-75.975297</v>
-      </c>
-      <c r="I12" t="n">
-        <v>1257</v>
-      </c>
-      <c r="J12" t="n">
-        <v>52</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-9.28735</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-75.975297</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1257</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -1093,20 +1191,30 @@
           <t>021 AMAZONAS / AMAZONAS</t>
         </is>
       </c>
-      <c r="G13" t="n">
-        <v>-9.2934</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-75.99527</v>
-      </c>
-      <c r="I13" t="n">
-        <v>611</v>
-      </c>
-      <c r="J13" t="n">
-        <v>36</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0</v>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-9.2934</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>-75.99527</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -1145,20 +1253,30 @@
           <t>LA SAGRADA FAMILIA FE Y ALEGRIA 64</t>
         </is>
       </c>
-      <c r="G14" t="n">
-        <v>-9.302512999999999</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-76.00295300000001</v>
-      </c>
-      <c r="I14" t="n">
-        <v>747</v>
-      </c>
-      <c r="J14" t="n">
-        <v>35</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-9.302513</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-76.002953</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -1197,20 +1315,30 @@
           <t>LAS ABEJITAS</t>
         </is>
       </c>
-      <c r="G15" t="n">
-        <v>-9.30261</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-76.00044</v>
-      </c>
-      <c r="I15" t="n">
-        <v>63</v>
-      </c>
-      <c r="J15" t="n">
-        <v>4</v>
-      </c>
-      <c r="K15" t="n">
-        <v>1</v>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-9.30261</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-76.00044</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -1249,20 +1377,30 @@
           <t>PUMAHUASI</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>-9.188507</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-75.954673</v>
-      </c>
-      <c r="I16" t="n">
-        <v>376</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-9.188507</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-75.954673</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>376</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1301,20 +1439,30 @@
           <t>33164 FELIPE HUAMAN POMA DE AYALA</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>-9.088554</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-76.095462</v>
-      </c>
-      <c r="I17" t="n">
-        <v>407</v>
-      </c>
-      <c r="J17" t="n">
-        <v>26</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-9.088554</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-76.095462</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>407</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1353,20 +1501,30 @@
           <t>GALILEO GALILEI</t>
         </is>
       </c>
-      <c r="G18" t="n">
-        <v>-9.29144</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-75.99626000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>399</v>
-      </c>
-      <c r="J18" t="n">
-        <v>25</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-9.29144</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-75.99626</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>399</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1405,20 +1563,30 @@
           <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
-      <c r="G19" t="n">
-        <v>-9.307040000000001</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-76.00278</v>
-      </c>
-      <c r="I19" t="n">
-        <v>235</v>
-      </c>
-      <c r="J19" t="n">
-        <v>10</v>
-      </c>
-      <c r="K19" t="n">
-        <v>1</v>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-9.30704</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-76.00278</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1457,20 +1625,30 @@
           <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
-      <c r="G20" t="n">
-        <v>-9.303559999999999</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-76.00174</v>
-      </c>
-      <c r="I20" t="n">
-        <v>236</v>
-      </c>
-      <c r="J20" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" t="n">
-        <v>1</v>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-9.30356</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-76.00174</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1509,20 +1687,30 @@
           <t>CIENCIAS</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>-9.295629999999999</v>
-      </c>
-      <c r="H21" t="n">
-        <v>-76.000557</v>
-      </c>
-      <c r="I21" t="n">
-        <v>747</v>
-      </c>
-      <c r="J21" t="n">
-        <v>41</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-9.29563</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-76.000557</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>

--- a/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>201372</t>
+          <t>628483</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.29676</t>
+          <t>-9.30704</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-75.99981</t>
+          <t>-76.00278</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>235</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>201386</t>
+          <t>201372</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>017</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.306462</t>
+          <t>-9.29676</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-76.003079</t>
+          <t>-75.99981</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>379</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,32 +625,32 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>201720</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32262 LEONCIO PRADO GUTIERREZ</t>
+          <t>32916 ESTEBAN FLORES LLANOS</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.29647</t>
+          <t>-9.2944</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.9986</t>
+          <t>-75.9939</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>325</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>201503</t>
+          <t>630103</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>32483 RICARDO PALMA SORIANO</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.30252</t>
+          <t>-9.30356</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.0023</t>
+          <t>-76.00174</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>236</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>19</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>201720</t>
+          <t>202456</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>32916 ESTEBAN FLORES LLANOS</t>
+          <t>PUMAHUASI</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.2944</t>
+          <t>-9.188507</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.9939</t>
+          <t>-75.954673</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>376</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>201824</t>
+          <t>590376</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>GALILEO GALILEI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.278459</t>
+          <t>-9.29144</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-76.009296</t>
+          <t>-75.99626</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>399</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>201838</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>GOMEZ ARIAS DAVILA</t>
+          <t>33164 FELIPE HUAMAN POMA DE AYALA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.30587</t>
+          <t>-9.088554</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.00341</t>
+          <t>-76.095462</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>407</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>201857</t>
+          <t>201386</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MARIANO BONIN</t>
+          <t>018</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.29221</t>
+          <t>-9.306462</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-75.99722</t>
+          <t>-76.003079</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>52</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>201862</t>
+          <t>201490</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MARISCAL RAMON CASTILLA</t>
+          <t>32262 LEONCIO PRADO GUTIERREZ</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.30245</t>
+          <t>-9.29647</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-76.00537</t>
+          <t>-75.9986</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>855</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>201876</t>
+          <t>202140</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>PADRE ABAD</t>
+          <t>LA SAGRADA FAMILIA FE Y ALEGRIA 64</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.29977</t>
+          <t>-9.302513</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-75.9995</t>
+          <t>-76.002953</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>747</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>201881</t>
+          <t>202022</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SAN JORGE</t>
+          <t>021 AMAZONAS / AMAZONAS</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.28735</t>
+          <t>-9.2934</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.975297</t>
+          <t>-75.99527</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>611</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>202022</t>
+          <t>202159</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>021 AMAZONAS / AMAZONAS</t>
+          <t>LAS ABEJITAS</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.2934</t>
+          <t>-9.30261</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-75.99527</t>
+          <t>-76.00044</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>63</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,22 +1245,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>202140</t>
+          <t>630462</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA FE Y ALEGRIA 64</t>
+          <t>CIENCIAS</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.302513</t>
+          <t>-9.29563</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.002953</t>
+          <t>-76.000557</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>41</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,37 +1307,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>202159</t>
+          <t>201824</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>LAS ABEJITAS</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.30261</t>
+          <t>-9.278459</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.00044</t>
+          <t>-76.009296</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>968</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>202456</t>
+          <t>201881</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PUMAHUASI</t>
+          <t>SAN JORGE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.188507</t>
+          <t>-9.28735</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.954673</t>
+          <t>-75.975297</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>201862</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>33164 FELIPE HUAMAN POMA DE AYALA</t>
+          <t>MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.088554</t>
+          <t>-9.30245</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.095462</t>
+          <t>-76.00537</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>58</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>590376</t>
+          <t>201876</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>GALILEO GALILEI</t>
+          <t>PADRE ABAD</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.29144</t>
+          <t>-9.29977</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.99626</t>
+          <t>-75.9995</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,37 +1555,37 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>628483</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>MARIANO BONIN</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.30704</t>
+          <t>-9.29221</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.00278</t>
+          <t>-75.99722</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>63</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>630103</t>
+          <t>201503</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>32483 RICARDO PALMA SORIANO</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.30356</t>
+          <t>-9.30252</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.00174</t>
+          <t>-76.0023</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>64</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>630462</t>
+          <t>201838</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CIENCIAS</t>
+          <t>GOMEZ ARIAS DAVILA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.29563</t>
+          <t>-9.30587</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.000557</t>
+          <t>-76.00341</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>76</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
@@ -501,37 +501,37 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>628483</t>
+          <t>630462</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>SAN IGNACIO DE LOYOLA</t>
+          <t>CIENCIAS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-9.30704</t>
+          <t>747</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-76.00278</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>235</t>
+          <t>-9.29563</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-76.000557</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -563,37 +563,37 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>201372</t>
+          <t>630103</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>017</t>
+          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-9.29676</t>
+          <t>236</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-75.99981</t>
+          <t>19</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>-9.30356</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>-76.00174</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -625,37 +625,37 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>201720</t>
+          <t>628483</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>32916 ESTEBAN FLORES LLANOS</t>
+          <t>SAN IGNACIO DE LOYOLA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-9.2944</t>
+          <t>235</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-75.9939</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>-9.30704</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>-76.00278</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>630103</t>
+          <t>590376</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>SANTIAGO ANTUNEZ DE MAYOLO</t>
+          <t>GALILEO GALILEI</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-9.30356</t>
+          <t>399</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-76.00174</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>-9.29144</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>-75.99626</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -749,32 +749,32 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>202456</t>
+          <t>202611</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PUMAHUASI</t>
+          <t>33164 FELIPE HUAMAN POMA DE AYALA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-9.188507</t>
+          <t>407</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-75.954673</t>
+          <t>26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>-9.088554</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>-76.095462</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>590376</t>
+          <t>202456</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>GALILEO GALILEI</t>
+          <t>PUMAHUASI</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-9.29144</t>
+          <t>376</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-75.99626</t>
+          <t>24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>399</t>
+          <t>-9.188507</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-75.954673</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -873,37 +873,37 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>202611</t>
+          <t>202159</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>33164 FELIPE HUAMAN POMA DE AYALA</t>
+          <t>LAS ABEJITAS</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-9.088554</t>
+          <t>63</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-76.095462</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>407</t>
+          <t>-9.30261</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>-76.00044</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -935,37 +935,37 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>201386</t>
+          <t>202140</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>018</t>
+          <t>LA SAGRADA FAMILIA FE Y ALEGRIA 64</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-9.306462</t>
+          <t>747</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-76.003079</t>
+          <t>35</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-9.302513</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-76.002953</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -997,32 +997,32 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>202022</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>32262 LEONCIO PRADO GUTIERREZ</t>
+          <t>021 AMAZONAS / AMAZONAS</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-9.29647</t>
+          <t>611</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-75.9986</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>855</t>
+          <t>-9.2934</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>-75.99527</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1059,32 +1059,32 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>202140</t>
+          <t>201881</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>LA SAGRADA FAMILIA FE Y ALEGRIA 64</t>
+          <t>SAN JORGE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-9.302513</t>
+          <t>1257</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-76.002953</t>
+          <t>52</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>-9.28735</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>-75.975297</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1121,32 +1121,32 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>202022</t>
+          <t>201876</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>021 AMAZONAS / AMAZONAS</t>
+          <t>PADRE ABAD</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-9.2934</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-75.99527</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>-9.29977</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>-75.9995</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1183,37 +1183,37 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>202159</t>
+          <t>201862</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>LAS ABEJITAS</t>
+          <t>MARISCAL RAMON CASTILLA</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-9.30261</t>
+          <t>1494</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-76.00044</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-9.30245</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-76.00537</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1245,32 +1245,32 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>630462</t>
+          <t>201857</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>CIENCIAS</t>
+          <t>MARIANO BONIN</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-9.29563</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.000557</t>
+          <t>63</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>747</t>
+          <t>-9.29221</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>-75.99722</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1307,32 +1307,32 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>201824</t>
+          <t>201838</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CESAR VALLEJO</t>
+          <t>GOMEZ ARIAS DAVILA</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-9.278459</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-76.009296</t>
+          <t>76</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>968</t>
+          <t>-9.30587</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>-76.00341</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1369,32 +1369,32 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>201881</t>
+          <t>201824</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SAN JORGE</t>
+          <t>CESAR VALLEJO</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-9.28735</t>
+          <t>968</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-75.975297</t>
+          <t>44</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1257</t>
+          <t>-9.278459</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>-76.009296</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1431,32 +1431,32 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>201862</t>
+          <t>201720</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>MARISCAL RAMON CASTILLA</t>
+          <t>32916 ESTEBAN FLORES LLANOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-9.30245</t>
+          <t>325</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-76.00537</t>
+          <t>16</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1494</t>
+          <t>-9.2944</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>-75.9939</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -1493,32 +1493,32 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>201876</t>
+          <t>201503</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>PADRE ABAD</t>
+          <t>32483 RICARDO PALMA SORIANO</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.29977</t>
+          <t>1655</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-75.9995</t>
+          <t>64</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>-9.30252</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>-76.0023</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>201857</t>
+          <t>201490</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>MARIANO BONIN</t>
+          <t>32262 LEONCIO PRADO GUTIERREZ</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.29221</t>
+          <t>855</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-75.99722</t>
+          <t>34</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>-9.29647</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>-75.9986</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -1617,37 +1617,37 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>201503</t>
+          <t>201386</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>32483 RICARDO PALMA SORIANO</t>
+          <t>018</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-9.30252</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-76.0023</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1655</t>
+          <t>-9.306462</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>-76.003079</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1679,32 +1679,32 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>201838</t>
+          <t>201372</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>GOMEZ ARIAS DAVILA</t>
+          <t>017</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-9.30587</t>
+          <t>379</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-76.00341</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>-9.29676</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>-75.99981</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">

--- a/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
+++ b/ZonasEscolares/excels/HUANUCO-LEONCIO_PRADO-RUPA-RUPA.xlsx
@@ -449,22 +449,22 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>alumnos</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>docentes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>latitud</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>longitud</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>alumnos</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>docentes</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
